--- a/AAII_Financials/Quarterly/WRPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WRPT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
   <si>
     <t>WRPT</t>
   </si>
@@ -656,78 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45138</v>
+      </c>
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -770,8 +782,17 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -814,8 +835,17 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,8 +888,17 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +915,11 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,8 +962,17 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,8 +1015,17 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,8 +1068,17 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1052,8 +1121,17 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,52 +1145,64 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>100</v>
       </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
       <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>100</v>
       </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1126,37 +1216,46 @@
         <v>0</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,8 +1272,11 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1205,20 +1307,29 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1237,32 +1348,41 @@
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1305,52 +1425,70 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1393,8 +1531,17 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,96 +1584,123 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1743,17 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1796,17 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1849,17 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,8 +1902,17 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1733,64 +1943,82 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
+        <v>0</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,101 +2061,128 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45138</v>
+      </c>
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2199,11 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,8 +2220,11 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1983,31 +2244,40 @@
         <v>0</v>
       </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
+        <v>0</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2050,8 +2320,17 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2094,8 +2373,17 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2138,8 +2426,17 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2167,14 +2464,14 @@
       <c r="K45" s="3">
         <v>0</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
@@ -2182,8 +2479,17 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2203,31 +2509,40 @@
         <v>0</v>
       </c>
       <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>0</v>
+      </c>
+      <c r="K46" s="3">
+        <v>0</v>
+      </c>
+      <c r="L46" s="3">
         <v>100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>100</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
+      <c r="O46" s="3">
+        <v>0</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2270,8 +2585,17 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2314,8 +2638,17 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2329,16 +2662,16 @@
         <v>200</v>
       </c>
       <c r="G49" s="3">
+        <v>200</v>
+      </c>
+      <c r="H49" s="3">
+        <v>200</v>
+      </c>
+      <c r="I49" s="3">
+        <v>200</v>
+      </c>
+      <c r="J49" s="3">
         <v>300</v>
-      </c>
-      <c r="H49" s="3">
-        <v>300</v>
-      </c>
-      <c r="I49" s="3">
-        <v>300</v>
-      </c>
-      <c r="J49" s="3">
-        <v>600</v>
       </c>
       <c r="K49" s="3">
         <v>300</v>
@@ -2346,20 +2679,29 @@
       <c r="L49" s="3">
         <v>300</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>600</v>
+      </c>
+      <c r="N49" s="3">
+        <v>300</v>
+      </c>
+      <c r="O49" s="3">
+        <v>300</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2744,17 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,8 +2797,17 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2463,20 +2823,20 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2490,8 +2850,17 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,8 +2903,17 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2549,37 +2927,46 @@
         <v>200</v>
       </c>
       <c r="G54" s="3">
+        <v>200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>200</v>
+      </c>
+      <c r="I54" s="3">
+        <v>200</v>
+      </c>
+      <c r="J54" s="3">
         <v>300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>300</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2983,11 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,13 +3004,16 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
@@ -2629,16 +3022,16 @@
         <v>0</v>
       </c>
       <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -2646,20 +3039,29 @@
       <c r="L57" s="3">
         <v>0</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
+        <v>100</v>
+      </c>
+      <c r="O57" s="3">
+        <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2702,8 +3104,17 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2728,31 +3139,40 @@
       <c r="J59" s="3">
         <v>0</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
+      <c r="K59" s="3">
+        <v>0</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
+      <c r="M59" s="3">
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>0</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E60" s="3">
         <v>0</v>
@@ -2761,37 +3181,46 @@
         <v>0</v>
       </c>
       <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3">
         <v>100</v>
-      </c>
-      <c r="H60" s="3">
-        <v>100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
-        <v>200</v>
       </c>
       <c r="K60" s="3">
         <v>100</v>
       </c>
       <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3">
+        <v>200</v>
+      </c>
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
+      <c r="O60" s="3">
+        <v>100</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2814,28 +3243,37 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2851,24 +3289,24 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2878,8 +3316,17 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3369,17 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3422,17 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,13 +3475,22 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E66" s="3">
         <v>0</v>
@@ -3025,37 +3499,46 @@
         <v>0</v>
       </c>
       <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3">
         <v>100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>100</v>
       </c>
-      <c r="I66" s="3">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3">
         <v>600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>300</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3555,11 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3602,17 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3655,17 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3708,17 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,8 +3761,17 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3257,43 +3779,52 @@
         <v>-500</v>
       </c>
       <c r="E72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="F72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="G72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="H72" s="3">
         <v>-400</v>
       </c>
       <c r="I72" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K72" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L72" s="3">
         <v>-100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>-100</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
+        <v>0</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3867,17 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3920,17 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,8 +3973,17 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -3445,31 +4003,40 @@
         <v>200</v>
       </c>
       <c r="I76" s="3">
+        <v>200</v>
+      </c>
+      <c r="J76" s="3">
+        <v>200</v>
+      </c>
+      <c r="K76" s="3">
+        <v>200</v>
+      </c>
+      <c r="L76" s="3">
         <v>400</v>
       </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
-      <c r="K76" s="3">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3">
-        <v>0</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
+      <c r="M76" s="3">
+        <v>0</v>
+      </c>
+      <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
+        <v>0</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,101 +4079,128 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45138</v>
+      </c>
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
+        <v>0</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,8 +4217,11 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3667,8 +4264,17 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +4317,17 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +4370,17 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4423,17 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4476,17 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,8 +4529,17 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3899,40 +4550,49 @@
         <v>0</v>
       </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,8 +4609,11 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3961,22 +4624,22 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3993,8 +4656,17 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4709,17 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,8 +4762,17 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4093,40 +4783,49 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4842,11 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4187,8 +4889,17 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4942,17 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4995,17 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,52 +5048,70 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4407,8 +5154,17 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4425,30 +5181,39 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WRPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WRPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>WRPT</t>
   </si>
@@ -656,79 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -738,8 +738,11 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -791,8 +794,11 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -844,8 +850,11 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -897,8 +906,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,8 +930,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -971,8 +984,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,8 +1040,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1077,8 +1096,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,8 +1152,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,8 +1173,9 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1163,11 +1189,11 @@
         <v>0</v>
       </c>
       <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
         <v>100</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
       <c r="I17" s="3">
         <v>0</v>
       </c>
@@ -1175,22 +1201,22 @@
         <v>0</v>
       </c>
       <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
       <c r="N17" s="3">
         <v>0</v>
       </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
+      <c r="P17" s="3">
+        <v>0</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
@@ -1201,8 +1227,11 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1216,11 +1245,11 @@
         <v>0</v>
       </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
         <v>0</v>
       </c>
@@ -1228,22 +1257,22 @@
         <v>0</v>
       </c>
       <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
       <c r="N18" s="3">
         <v>0</v>
       </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
+      <c r="P18" s="3">
+        <v>0</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
@@ -1254,8 +1283,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,8 +1307,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1316,8 +1349,8 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1328,8 +1361,11 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1357,20 +1393,20 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
         <v>0</v>
       </c>
       <c r="O21" s="3">
         <v>0</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
+      <c r="P21" s="3">
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
@@ -1381,8 +1417,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1434,8 +1473,11 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1449,11 +1491,11 @@
         <v>0</v>
       </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
         <v>0</v>
       </c>
@@ -1461,22 +1503,22 @@
         <v>0</v>
       </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>-300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
         <v>0</v>
       </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
+      <c r="P23" s="3">
+        <v>0</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
@@ -1487,8 +1529,11 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1540,8 +1585,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,8 +1641,11 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1608,11 +1659,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
         <v>0</v>
       </c>
@@ -1620,22 +1671,22 @@
         <v>0</v>
       </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
         <v>0</v>
       </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
+      <c r="P26" s="3">
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
@@ -1646,8 +1697,11 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1661,11 +1715,11 @@
         <v>0</v>
       </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
         <v>0</v>
       </c>
@@ -1673,22 +1727,22 @@
         <v>0</v>
       </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
         <v>0</v>
       </c>
       <c r="O27" s="3">
         <v>0</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
+      <c r="P27" s="3">
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
@@ -1699,8 +1753,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1809,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1865,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1921,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,8 +1977,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1952,8 +2021,8 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -1964,8 +2033,11 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1979,11 +2051,11 @@
         <v>0</v>
       </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
         <v>0</v>
       </c>
@@ -1991,22 +2063,22 @@
         <v>0</v>
       </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
         <v>0</v>
       </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
+      <c r="P33" s="3">
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
@@ -2017,8 +2089,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,8 +2145,11 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2085,11 +2163,11 @@
         <v>0</v>
       </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
         <v>0</v>
       </c>
@@ -2097,22 +2175,22 @@
         <v>0</v>
       </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
         <v>0</v>
       </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
+      <c r="P35" s="3">
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
@@ -2123,55 +2201,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2181,8 +2262,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2286,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,8 +2308,9 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2253,19 +2339,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
+      <c r="P41" s="3">
+        <v>0</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
@@ -2276,8 +2362,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,8 +2418,11 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2382,8 +2474,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2435,8 +2530,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2473,8 +2571,8 @@
       <c r="N45" s="3">
         <v>0</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
@@ -2488,8 +2586,11 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2518,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="L46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M46" s="3">
         <v>100</v>
@@ -2527,10 +2628,10 @@
         <v>100</v>
       </c>
       <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
@@ -2541,8 +2642,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2594,8 +2698,11 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2647,8 +2754,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2671,7 +2781,7 @@
         <v>200</v>
       </c>
       <c r="J49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K49" s="3">
         <v>300</v>
@@ -2680,16 +2790,16 @@
         <v>300</v>
       </c>
       <c r="M49" s="3">
+        <v>300</v>
+      </c>
+      <c r="N49" s="3">
         <v>600</v>
-      </c>
-      <c r="N49" s="3">
-        <v>300</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>300</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -2700,8 +2810,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2866,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,40 +2922,43 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2859,8 +2978,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,8 +3034,11 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2936,26 +3061,26 @@
         <v>200</v>
       </c>
       <c r="J54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K54" s="3">
         <v>300</v>
       </c>
       <c r="L54" s="3">
+        <v>300</v>
+      </c>
+      <c r="M54" s="3">
         <v>400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>300</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3090,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3114,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,8 +3136,9 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3016,7 +3146,7 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
@@ -3031,25 +3161,25 @@
         <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
       </c>
       <c r="L57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
+      <c r="P57" s="3">
+        <v>0</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
@@ -3060,8 +3190,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3113,8 +3246,11 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3148,14 +3284,14 @@
       <c r="M59" s="3">
         <v>0</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
@@ -3166,8 +3302,11 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3175,7 +3314,7 @@
         <v>100</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F60" s="3">
         <v>0</v>
@@ -3190,25 +3329,25 @@
         <v>0</v>
       </c>
       <c r="J60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K60" s="3">
         <v>100</v>
       </c>
       <c r="L60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3">
         <v>200</v>
-      </c>
-      <c r="N60" s="3">
-        <v>100</v>
       </c>
       <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
+      <c r="P60" s="3">
+        <v>100</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
@@ -3219,8 +3358,11 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3252,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>300</v>
@@ -3261,7 +3403,7 @@
         <v>300</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -3272,13 +3414,16 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>0</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>3</v>
@@ -3298,18 +3443,18 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,8 +3470,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3526,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3582,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,8 +3638,11 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3493,7 +3650,7 @@
         <v>100</v>
       </c>
       <c r="E66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F66" s="3">
         <v>0</v>
@@ -3508,25 +3665,25 @@
         <v>0</v>
       </c>
       <c r="J66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K66" s="3">
         <v>100</v>
       </c>
       <c r="L66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M66" s="3">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3">
         <v>600</v>
-      </c>
-      <c r="N66" s="3">
-        <v>300</v>
       </c>
       <c r="O66" s="3">
         <v>300</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
+      <c r="P66" s="3">
+        <v>300</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
@@ -3537,8 +3694,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3718,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3772,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3828,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3884,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,8 +3940,11 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3788,7 +3961,7 @@
         <v>-500</v>
       </c>
       <c r="H72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="I72" s="3">
         <v>-400</v>
@@ -3800,19 +3973,19 @@
         <v>-400</v>
       </c>
       <c r="L72" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="M72" s="3">
         <v>-100</v>
       </c>
       <c r="N72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O72" s="3">
         <v>0</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
+      <c r="P72" s="3">
+        <v>0</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
@@ -3823,8 +3996,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4052,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4108,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,8 +4164,11 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4012,19 +4197,19 @@
         <v>200</v>
       </c>
       <c r="L76" s="3">
+        <v>200</v>
+      </c>
+      <c r="M76" s="3">
         <v>400</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
       <c r="N76" s="3">
         <v>0</v>
       </c>
       <c r="O76" s="3">
         <v>0</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
+      <c r="P76" s="3">
+        <v>0</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
@@ -4035,8 +4220,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,55 +4276,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4146,8 +4337,11 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4161,11 +4355,11 @@
         <v>0</v>
       </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
         <v>0</v>
       </c>
@@ -4173,22 +4367,22 @@
         <v>0</v>
       </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
         <v>0</v>
       </c>
       <c r="O81" s="3">
         <v>0</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
+      <c r="P81" s="3">
+        <v>0</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
@@ -4199,8 +4393,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,8 +4417,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4273,8 +4471,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4527,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4583,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4639,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4695,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,8 +4751,11 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4559,28 +4775,28 @@
         <v>0</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>300</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
@@ -4591,8 +4807,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,8 +4831,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4630,10 +4850,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-300</v>
       </c>
       <c r="J91" s="3">
         <v>-300</v>
@@ -4642,7 +4862,7 @@
         <v>-300</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4665,8 +4885,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4941,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,8 +4997,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4792,28 +5021,28 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>200</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-300</v>
       </c>
       <c r="N94" s="3">
         <v>-300</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -4824,8 +5053,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5077,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4898,8 +5131,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5187,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5243,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,8 +5299,11 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5071,11 +5316,11 @@
       <c r="F100" s="3">
         <v>0</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
@@ -5084,22 +5329,22 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
@@ -5110,8 +5355,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5163,8 +5411,11 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5190,11 +5441,11 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
@@ -5204,8 +5455,8 @@
       <c r="O102" s="3">
         <v>0</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
@@ -5214,6 +5465,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WRPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WRPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>WRPT</t>
   </si>
@@ -656,82 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -741,8 +742,11 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -797,8 +801,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -853,8 +860,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -909,8 +919,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,8 +944,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -987,8 +1001,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1060,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1099,8 +1119,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1155,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,13 +1200,14 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -1192,11 +1219,11 @@
         <v>0</v>
       </c>
       <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
         <v>100</v>
       </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
       <c r="J17" s="3">
         <v>0</v>
       </c>
@@ -1204,22 +1231,22 @@
         <v>0</v>
       </c>
       <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
       <c r="P17" s="3">
         <v>0</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
+      <c r="Q17" s="3">
+        <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
@@ -1230,8 +1257,11 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1248,11 +1278,11 @@
         <v>0</v>
       </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
         <v>0</v>
       </c>
@@ -1260,22 +1290,22 @@
         <v>0</v>
       </c>
       <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
       <c r="P18" s="3">
         <v>0</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
+      <c r="Q18" s="3">
+        <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
@@ -1286,8 +1316,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,8 +1341,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1352,8 +1386,8 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1364,8 +1398,11 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1396,20 +1433,20 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
         <v>0</v>
       </c>
       <c r="P21" s="3">
         <v>0</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
+      <c r="Q21" s="3">
+        <v>0</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
@@ -1420,8 +1457,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1476,13 +1516,16 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -1494,11 +1537,11 @@
         <v>0</v>
       </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
@@ -1506,22 +1549,22 @@
         <v>0</v>
       </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
       <c r="P23" s="3">
         <v>0</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
+      <c r="Q23" s="3">
+        <v>0</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
@@ -1532,8 +1575,11 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1588,8 +1634,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,13 +1693,16 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
@@ -1662,11 +1714,11 @@
         <v>0</v>
       </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
         <v>0</v>
       </c>
@@ -1674,22 +1726,22 @@
         <v>0</v>
       </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
       <c r="P26" s="3">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
+      <c r="Q26" s="3">
+        <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
@@ -1700,13 +1752,16 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
@@ -1718,11 +1773,11 @@
         <v>0</v>
       </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
@@ -1730,22 +1785,22 @@
         <v>0</v>
       </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
         <v>0</v>
       </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
+      <c r="Q27" s="3">
+        <v>0</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
@@ -1756,8 +1811,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,8 +2047,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2024,8 +2094,8 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2036,13 +2106,16 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
@@ -2054,11 +2127,11 @@
         <v>0</v>
       </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
@@ -2066,22 +2139,22 @@
         <v>0</v>
       </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
       <c r="P33" s="3">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
+      <c r="Q33" s="3">
+        <v>0</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
@@ -2092,8 +2165,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,13 +2224,16 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
@@ -2166,11 +2245,11 @@
         <v>0</v>
       </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
         <v>0</v>
       </c>
@@ -2178,22 +2257,22 @@
         <v>0</v>
       </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
       <c r="P35" s="3">
         <v>0</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
+      <c r="Q35" s="3">
+        <v>0</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
@@ -2204,58 +2283,61 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2265,8 +2347,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,8 +2395,9 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2342,19 +2429,19 @@
         <v>0</v>
       </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
+      <c r="Q41" s="3">
+        <v>0</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
@@ -2365,8 +2452,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2421,8 +2511,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2477,8 +2570,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2533,8 +2629,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2574,8 +2673,8 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
+      <c r="P45" s="3">
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
@@ -2589,8 +2688,11 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2622,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N46" s="3">
         <v>100</v>
@@ -2631,10 +2733,10 @@
         <v>100</v>
       </c>
       <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>0</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
@@ -2645,8 +2747,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2701,31 +2806,34 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
         <v>0</v>
       </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -2757,8 +2865,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2784,7 +2895,7 @@
         <v>200</v>
       </c>
       <c r="K49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L49" s="3">
         <v>300</v>
@@ -2793,16 +2904,16 @@
         <v>300</v>
       </c>
       <c r="N49" s="3">
+        <v>300</v>
+      </c>
+      <c r="O49" s="3">
         <v>600</v>
-      </c>
-      <c r="O49" s="3">
-        <v>300</v>
       </c>
       <c r="P49" s="3">
         <v>300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>300</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -2813,8 +2924,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,8 +3042,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2951,17 +3071,17 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,8 +3160,11 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3064,26 +3190,26 @@
         <v>200</v>
       </c>
       <c r="K54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L54" s="3">
         <v>300</v>
       </c>
       <c r="M54" s="3">
+        <v>300</v>
+      </c>
+      <c r="N54" s="3">
         <v>400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,8 +3267,9 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3149,7 +3280,7 @@
         <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
         <v>0</v>
@@ -3164,25 +3295,25 @@
         <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
+      <c r="Q57" s="3">
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
@@ -3193,8 +3324,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3249,8 +3383,11 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3287,14 +3424,14 @@
       <c r="N59" s="3">
         <v>0</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>0</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
@@ -3305,8 +3442,11 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3317,7 +3457,7 @@
         <v>100</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G60" s="3">
         <v>0</v>
@@ -3332,25 +3472,25 @@
         <v>0</v>
       </c>
       <c r="K60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L60" s="3">
         <v>100</v>
       </c>
       <c r="M60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3">
         <v>200</v>
-      </c>
-      <c r="O60" s="3">
-        <v>100</v>
       </c>
       <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
+      <c r="Q60" s="3">
+        <v>100</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
@@ -3361,8 +3501,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3397,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>300</v>
@@ -3406,7 +3549,7 @@
         <v>300</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -3417,16 +3560,19 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -3446,18 +3592,18 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,8 +3796,11 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3653,7 +3811,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G66" s="3">
         <v>0</v>
@@ -3668,25 +3826,25 @@
         <v>0</v>
       </c>
       <c r="K66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L66" s="3">
         <v>100</v>
       </c>
       <c r="M66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N66" s="3">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3">
         <v>600</v>
-      </c>
-      <c r="O66" s="3">
-        <v>300</v>
       </c>
       <c r="P66" s="3">
         <v>300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
+      <c r="Q66" s="3">
+        <v>300</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,13 +4114,16 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="E72" s="3">
         <v>-500</v>
@@ -3964,7 +4138,7 @@
         <v>-500</v>
       </c>
       <c r="I72" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="J72" s="3">
         <v>-400</v>
@@ -3976,19 +4150,19 @@
         <v>-400</v>
       </c>
       <c r="M72" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="N72" s="3">
         <v>-100</v>
       </c>
       <c r="O72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P72" s="3">
         <v>0</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
+      <c r="Q72" s="3">
+        <v>0</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,8 +4350,11 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4200,19 +4386,19 @@
         <v>200</v>
       </c>
       <c r="M76" s="3">
+        <v>200</v>
+      </c>
+      <c r="N76" s="3">
         <v>400</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
       <c r="O76" s="3">
         <v>0</v>
       </c>
       <c r="P76" s="3">
         <v>0</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
+      <c r="Q76" s="3">
+        <v>0</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,58 +4468,61 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4340,13 +4532,16 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
@@ -4358,11 +4553,11 @@
         <v>0</v>
       </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
         <v>0</v>
       </c>
@@ -4370,22 +4565,22 @@
         <v>0</v>
       </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
         <v>0</v>
       </c>
       <c r="P81" s="3">
         <v>0</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
+      <c r="Q81" s="3">
+        <v>0</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
@@ -4396,8 +4591,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4616,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4474,8 +4673,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,13 +4968,16 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
@@ -4778,28 +4995,28 @@
         <v>0</v>
       </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>300</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
@@ -4810,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,8 +5052,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4853,10 +5074,10 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
@@ -4865,7 +5086,7 @@
         <v>-300</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -4888,8 +5109,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,8 +5227,11 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5024,28 +5254,28 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>200</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-300</v>
       </c>
       <c r="O94" s="3">
         <v>-300</v>
       </c>
       <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5056,8 +5286,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5134,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,13 +5545,16 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -5322,32 +5568,32 @@
       <c r="H100" s="3">
         <v>0</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
@@ -5358,8 +5604,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5414,8 +5663,11 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5444,11 +5696,11 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
@@ -5458,8 +5710,8 @@
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
@@ -5468,6 +5720,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
